--- a/data/ams_weekly_data/White_Mulberry/business_report_week16.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/business_report_week16.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\Weekly 16\Weekly 16\ams_weekly_data\White_Mulberry\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\ams_weekly_data\White_Mulberry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8228723D-EB80-4E59-9B49-38DA29FB4398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{278CEBB7-0398-4F58-B018-819972318C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="131">
   <si>
     <t>(Parent) ASIN</t>
   </si>
@@ -415,12 +415,6 @@
   </si>
   <si>
     <t>WM-SMD09-WH</t>
-  </si>
-  <si>
-    <t>B0DS2HLR6S</t>
-  </si>
-  <si>
-    <t>White Mulberry Motorized Desk Drawer Variation</t>
   </si>
   <si>
     <t>FBA79616</t>
@@ -808,7 +802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X39"/>
+  <dimension ref="A1:X38"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="19" width="8.88671875" style="1"/>
@@ -2760,44 +2754,44 @@
       <c r="X27"/>
     </row>
     <row r="28" spans="1:24" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B28" t="e">
-        <v>#N/A</v>
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" t="s">
+        <v>24</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>25</v>
       </c>
       <c r="D28" t="s">
-        <v>127</v>
+        <v>25</v>
       </c>
       <c r="E28" t="s">
-        <v>128</v>
+        <v>26</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>134</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H28" s="5">
-        <v>2.9999999999999997E-4</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="I28" s="5">
-        <v>0</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="J28">
-        <v>1</v>
+        <v>177</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L28" s="5">
-        <v>2.0000000000000001E-4</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="M28" s="5">
-        <v>0</v>
+        <v>1.5E-3</v>
       </c>
       <c r="N28" s="5">
         <v>0</v>
@@ -2833,49 +2827,49 @@
     </row>
     <row r="29" spans="1:24" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D29" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E29" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F29">
-        <v>134</v>
+        <v>268</v>
       </c>
       <c r="G29">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H29" s="5">
-        <v>8.9999999999999998E-4</v>
+        <v>1.8E-3</v>
       </c>
       <c r="I29" s="5">
-        <v>1.1999999999999999E-3</v>
+        <v>3.7000000000000002E-3</v>
       </c>
       <c r="J29">
-        <v>177</v>
+        <v>344</v>
       </c>
       <c r="K29">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L29" s="5">
-        <v>8.9999999999999998E-4</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="M29" s="5">
-        <v>1.5E-3</v>
+        <v>2.8999999999999998E-3</v>
       </c>
       <c r="N29" s="5">
-        <v>0</v>
+        <v>1.35E-2</v>
       </c>
       <c r="O29" s="5">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -2905,49 +2899,49 @@
     </row>
     <row r="30" spans="1:24" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C30" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D30" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E30" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F30">
-        <v>268</v>
+        <v>35</v>
       </c>
       <c r="G30">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H30" s="5">
-        <v>1.8E-3</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="I30" s="5">
-        <v>3.7000000000000002E-3</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="J30">
-        <v>344</v>
+        <v>42</v>
       </c>
       <c r="K30">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="L30" s="5">
-        <v>1.6999999999999999E-3</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="M30" s="5">
-        <v>2.8999999999999998E-3</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="N30" s="5">
-        <v>1.35E-2</v>
+        <v>0</v>
       </c>
       <c r="O30" s="5">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -2975,241 +2969,169 @@
       </c>
       <c r="X30"/>
     </row>
-    <row r="31" spans="1:24" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="C31" t="s">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="D31" t="s">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="E31" t="s">
-        <v>34</v>
-      </c>
-      <c r="F31">
-        <v>35</v>
-      </c>
-      <c r="G31">
-        <v>3</v>
-      </c>
-      <c r="H31" s="5">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="I31" s="5">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="J31">
-        <v>42</v>
-      </c>
-      <c r="K31">
-        <v>3</v>
-      </c>
-      <c r="L31" s="5">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="M31" s="5">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="N31" s="5">
-        <v>0</v>
-      </c>
-      <c r="O31" s="5">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="P31">
-        <v>0</v>
-      </c>
-      <c r="Q31">
-        <v>0</v>
-      </c>
-      <c r="R31" s="5">
-        <v>0</v>
-      </c>
-      <c r="S31" s="5">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="T31" s="6">
-        <v>0</v>
-      </c>
-      <c r="U31" s="6">
-        <v>0</v>
-      </c>
-      <c r="V31">
-        <v>0</v>
-      </c>
-      <c r="W31">
-        <v>0</v>
-      </c>
-      <c r="X31"/>
+        <v>110555.1</v>
+      </c>
     </row>
     <row r="32" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="E32" t="s">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="P32">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="T32" s="6">
-        <v>110555.1</v>
+        <v>41933.879999999997</v>
       </c>
     </row>
     <row r="33" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="D33" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="E33" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="P33">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="T33" s="6">
-        <v>41933.879999999997</v>
+        <v>13552.52</v>
       </c>
     </row>
     <row r="34" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="B34" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="C34" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="D34" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="E34" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="P34">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T34" s="6">
-        <v>13552.52</v>
+        <v>11946.6</v>
       </c>
     </row>
     <row r="35" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>108</v>
+        <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>32</v>
       </c>
       <c r="C35" t="s">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="D35" t="s">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="E35" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="P35">
         <v>3</v>
       </c>
       <c r="T35" s="6">
-        <v>11946.6</v>
+        <v>7878.81</v>
       </c>
     </row>
     <row r="36" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C36" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D36" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E36" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T36" s="6">
-        <v>7878.81</v>
+        <v>2710.16</v>
       </c>
     </row>
     <row r="37" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>27</v>
+        <v>127</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="C37" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="D37" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="E37" t="s">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="P37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T37" s="6">
-        <v>2710.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>129</v>
-      </c>
-      <c r="B38" t="s">
-        <v>130</v>
-      </c>
-      <c r="C38" t="s">
-        <v>131</v>
-      </c>
-      <c r="D38" t="s">
-        <v>131</v>
-      </c>
-      <c r="E38" t="s">
-        <v>132</v>
-      </c>
-      <c r="P38">
-        <v>0</v>
-      </c>
-      <c r="T38" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="P39"/>
+      <c r="P38"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ams_weekly_data/White_Mulberry/business_report_week16.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/business_report_week16.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,117 +417,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>(Parent) ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>(Child) ASIN</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Sessions - Total</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Sessions - Total - B2B</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Session Percentage - Total</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Session Percentage - Total - B2B</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Page Views - Total</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Page Views - Total - B2B</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Page Views Percentage - Total</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Page Views Percentage - Total - B2B</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Featured Offer Percentage</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Featured Offer Percentage - B2B</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>units_ordered</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Units Ordered - B2B</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Unit Session Percentage</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Unit Session Percentage - B2B</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>ordered_product_sales</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Ordered Product Sales - B2B</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Total Order Items</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Total Order Items - B2B</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/business_report_week16.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/business_report_week16.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,117 +429,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>(Parent) ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>(Child) ASIN</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Sessions - Total</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sessions - Total - B2B</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Session Percentage - Total</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Session Percentage - Total - B2B</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Page Views - Total</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Page Views - Total - B2B</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Page Views Percentage - Total</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Page Views Percentage - Total - B2B</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Featured Offer Percentage</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Featured Offer Percentage - B2B</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>units_ordered</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Units Ordered - B2B</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Unit Session Percentage</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Unit Session Percentage - B2B</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ordered_product_sales</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Ordered Product Sales - B2B</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Total Order Items</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Total Order Items - B2B</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/business_report_week16.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/business_report_week16.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,117 +417,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>(Parent) ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>(Child) ASIN</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Sessions - Total</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Sessions - Total - B2B</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Session Percentage - Total</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Session Percentage - Total - B2B</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Page Views - Total</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Page Views - Total - B2B</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Page Views Percentage - Total</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Page Views Percentage - Total - B2B</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Featured Offer Percentage</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Featured Offer Percentage - B2B</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>units_ordered</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Units Ordered - B2B</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Unit Session Percentage</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Unit Session Percentage - B2B</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>ordered_product_sales</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Ordered Product Sales - B2B</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Total Order Items</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Total Order Items - B2B</t>
         </is>
